--- a/Web Browsers Configuration/Firefox/about.config firefox.xlsx
+++ b/Web Browsers Configuration/Firefox/about.config firefox.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sense\Desktop\Firefox configurations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50cb2a26af6a7a83/CyberSecHome/Web Browsers Configuration/Firefox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE6A70E-23D5-410F-902C-F038E2EDDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{9EE6A70E-23D5-410F-902C-F038E2EDDAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7853C7D-5F23-4BF4-A416-4FE96C30EC43}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -555,13 +555,13 @@
     <t>SET BY registry</t>
   </si>
   <si>
-    <t>nglayout.debug.disable_xul_cache</t>
-  </si>
-  <si>
     <t>Block AI enhancements</t>
   </si>
   <si>
     <t>Checked</t>
+  </si>
+  <si>
+    <t>browser.cache.memory.capacity</t>
   </si>
 </sst>
 </file>
@@ -702,7 +702,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1170,8 +1170,12 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3"/>
-      <c r="B10" s="8"/>
+      <c r="A10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="8">
+        <v>4000000</v>
+      </c>
       <c r="C10" s="1"/>
       <c r="E10" s="4" t="s">
         <v>86</v>
@@ -1647,10 +1651,10 @@
       </c>
       <c r="C42" s="1"/>
       <c r="E42" t="s">
+        <v>176</v>
+      </c>
+      <c r="F42" s="16" t="s">
         <v>177</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2182,12 +2186,7 @@
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" t="s">
-        <v>176</v>
-      </c>
-      <c r="B105" s="14" t="b">
-        <v>1</v>
-      </c>
+      <c r="B105" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
